--- a/data/trans_dic/P15B_3_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P15B_3_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el trabajo en el último año</t>
+          <t>Población que ha tenido un accidente en el trabajo en el último año (tasa de respuesta: 89,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,62; 81,3</t>
+          <t>20,35; 81,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,95; 25,51</t>
+          <t>3,67; 24,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,69; 49,56</t>
+          <t>6,47; 46,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,43; 30,97</t>
+          <t>3,32; 28,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,3</t>
+          <t>0,0; 22,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,35; 39,82</t>
+          <t>7,13; 38,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,62; 20,18</t>
+          <t>3,5; 19,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,61; 50,96</t>
+          <t>10,66; 54,16</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,63; 18,76</t>
+          <t>4,23; 19,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,91; 34,23</t>
+          <t>11,14; 35,1</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,51; 20,8</t>
+          <t>5,12; 20,45</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 22,7</t>
+          <t>2,72; 23,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,29; 40,42</t>
+          <t>5,22; 40,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,97; 45,49</t>
+          <t>8,15; 55,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,39</t>
+          <t>0,0; 58,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,76</t>
+          <t>0,0; 38,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 3,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,11</t>
+          <t>0,0; 35,05</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 11,9</t>
+          <t>1,43; 12,07</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,66; 29,04</t>
+          <t>5,79; 30,61</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,74; 23,63</t>
+          <t>2,64; 22,81</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,7; 42,75</t>
+          <t>4,59; 39,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,18; 36,05</t>
+          <t>14,34; 36,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,04; 36,38</t>
+          <t>4,11; 38,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,12; 43,92</t>
+          <t>8,55; 44,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,21; 32,35</t>
+          <t>2,14; 29,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,06; 33,76</t>
+          <t>3,79; 31,67</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,0; 21,56</t>
+          <t>7,12; 21,28</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,55; 25,7</t>
+          <t>2,5; 22,64</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,22; 28,93</t>
+          <t>7,78; 29,77</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,78; 51,21</t>
+          <t>10,63; 51,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,48</t>
+          <t>0,0; 18,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,11; 32,94</t>
+          <t>4,85; 31,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,92; 70,85</t>
+          <t>17,25; 71,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,3; 20,81</t>
+          <t>2,15; 21,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,22</t>
+          <t>0,0; 26,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,99; 37,17</t>
+          <t>6,62; 36,1</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,13</t>
+          <t>0,0; 12,11</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,02; 20,09</t>
+          <t>4,8; 20,11</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,36; 48,94</t>
+          <t>10,85; 47,53</t>
         </is>
       </c>
     </row>
@@ -1277,32 +1277,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,18; 84,37</t>
+          <t>11,96; 86,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,23; 61,75</t>
+          <t>8,45; 62,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,84; 64,0</t>
+          <t>8,85; 63,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,08</t>
+          <t>0,0; 55,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,75</t>
+          <t>0,0; 43,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1312,27 +1312,27 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,44; 54,55</t>
+          <t>6,93; 56,51</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,12; 28,15</t>
+          <t>3,11; 25,61</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,93; 53,38</t>
+          <t>7,1; 54,11</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,98</t>
+          <t>0,0; 50,93</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26,93; 91,29</t>
+          <t>26,55; 90,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,89; 39,02</t>
+          <t>9,18; 39,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,62; 30,06</t>
+          <t>3,62; 32,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13,14; 46,5</t>
+          <t>12,64; 45,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,05</t>
+          <t>0,0; 40,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,77; 26,28</t>
+          <t>2,78; 27,31</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 5,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,83</t>
+          <t>0,0; 9,94</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,25; 61,95</t>
+          <t>16,28; 59,91</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7,65; 27,29</t>
+          <t>8,42; 27,95</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,54; 12,92</t>
+          <t>1,55; 14,08</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,5; 27,18</t>
+          <t>7,47; 28,2</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>18,98; 57,81</t>
+          <t>21,12; 59,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>30,51; 54,62</t>
+          <t>31,1; 55,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,1; 34,81</t>
+          <t>3,98; 34,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,38; 30,87</t>
+          <t>6,01; 30,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,41; 50,18</t>
+          <t>8,46; 50,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,11; 18,14</t>
+          <t>2,02; 17,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,91</t>
+          <t>0,0; 18,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,96; 19,52</t>
+          <t>5,08; 19,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19,33; 48,09</t>
+          <t>19,39; 49,35</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19,01; 35,29</t>
+          <t>18,38; 34,99</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,78; 20,02</t>
+          <t>3,85; 20,05</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,87; 20,93</t>
+          <t>7,48; 20,69</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,22; 49,09</t>
+          <t>11,46; 48,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,32</t>
+          <t>0,0; 29,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,48</t>
+          <t>0,0; 17,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13,03; 51,91</t>
+          <t>12,12; 49,93</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,88</t>
+          <t>0,0; 21,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,91</t>
+          <t>0,0; 34,54</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,76</t>
+          <t>0,0; 19,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,37; 27,94</t>
+          <t>2,38; 28,43</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,74; 27,68</t>
+          <t>7,96; 27,43</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,43; 26,3</t>
+          <t>2,47; 25,96</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,5; 12,75</t>
+          <t>1,55; 13,62</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9,04; 31,18</t>
+          <t>9,76; 32,29</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>24,11; 41,52</t>
+          <t>24,54; 40,91</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17,25; 27,12</t>
+          <t>16,98; 26,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10,22; 20,48</t>
+          <t>10,34; 20,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16,87; 30,55</t>
+          <t>17,21; 30,7</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,29; 18,96</t>
+          <t>5,01; 18,2</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,72; 9,26</t>
+          <t>2,57; 9,06</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,25; 11,95</t>
+          <t>4,14; 11,47</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,72; 11,74</t>
+          <t>4,69; 11,5</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>17,09; 29,47</t>
+          <t>16,95; 28,63</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11,11; 17,44</t>
+          <t>10,96; 17,35</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8,15; 14,55</t>
+          <t>8,14; 14,7</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>12,08; 19,7</t>
+          <t>11,54; 19,11</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el trabajo en el último año</t>
+          <t>Población que ha tenido un accidente en el trabajo en el último año (tasa de respuesta: 89,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1916; 7556</t>
+          <t>1892; 7536</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1094; 9447</t>
+          <t>1359; 8989</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1093; 9519</t>
+          <t>1242; 8985</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>964; 8700</t>
+          <t>932; 7962</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1872</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 6436</t>
+          <t>0; 6321</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2219; 12021</t>
+          <t>2153; 11593</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1340; 5847</t>
+          <t>1015; 5637</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1738; 8348</t>
+          <t>1746; 8872</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2347; 12131</t>
+          <t>2735; 12715</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5391; 16907</t>
+          <t>5501; 17339</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3143; 11869</t>
+          <t>2923; 11672</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1825</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>899; 7272</t>
+          <t>870; 7496</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>970; 7420</t>
+          <t>959; 7483</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1453; 11075</t>
+          <t>1983; 13544</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5055</t>
+          <t>0; 5253</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1989</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6154</t>
+          <t>0; 6134</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 1302</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 5568</t>
+          <t>0; 5893</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>920; 7412</t>
+          <t>888; 7518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1938; 9943</t>
+          <t>1982; 10480</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1579; 13633</t>
+          <t>1525; 13162</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>858; 7793</t>
+          <t>837; 7170</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7496; 19055</t>
+          <t>7578; 19269</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>939; 8452</t>
+          <t>956; 8928</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1945; 9369</t>
+          <t>1823; 9389</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1524</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 1954</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 1750</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>592; 8668</t>
+          <t>574; 8021</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>911; 7575</t>
+          <t>849; 7104</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7503; 20214</t>
+          <t>6674; 19953</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>947; 9540</t>
+          <t>928; 8402</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3474; 13922</t>
+          <t>3746; 14327</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1920; 9124</t>
+          <t>1893; 9143</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 7141</t>
+          <t>0; 5857</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1961; 12648</t>
+          <t>1862; 11928</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4255; 16828</t>
+          <t>4096; 16930</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1672</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 1837</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>836; 7569</t>
+          <t>783; 7671</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3864</t>
+          <t>0; 4757</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1929; 10263</t>
+          <t>1827; 9966</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 6459</t>
+          <t>0; 5959</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3756; 15021</t>
+          <t>3591; 15037</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4768; 20538</t>
+          <t>4552; 19945</t>
         </is>
       </c>
     </row>
@@ -3041,32 +3041,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>818; 6175</t>
+          <t>875; 6337</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1084; 8134</t>
+          <t>1113; 8194</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>895; 6479</t>
+          <t>896; 6397</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3847</t>
+          <t>0; 3947</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4508</t>
+          <t>0; 3397</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 1880</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -3076,27 +3076,27 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 417</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>974; 8250</t>
+          <t>1049; 8547</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1028; 9280</t>
+          <t>1026; 8444</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1016; 7824</t>
+          <t>1041; 7930</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 3901</t>
+          <t>0; 3897</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2395; 8118</t>
+          <t>2361; 8080</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2699; 11844</t>
+          <t>2787; 12046</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>993; 8242</t>
+          <t>992; 8940</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3422; 12105</t>
+          <t>3291; 11855</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4352</t>
+          <t>0; 4299</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>981; 9308</t>
+          <t>983; 9671</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 2108</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 2925</t>
+          <t>0; 2683</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3168; 12078</t>
+          <t>3174; 11679</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5034; 17945</t>
+          <t>5538; 18379</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>983; 8255</t>
+          <t>993; 8996</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3978; 14415</t>
+          <t>3962; 14952</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5178; 15773</t>
+          <t>5764; 16369</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>20062; 35910</t>
+          <t>20449; 36753</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1084; 9201</t>
+          <t>1052; 9225</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2335; 13411</t>
+          <t>2611; 13429</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>997; 9241</t>
+          <t>1557; 9262</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1240; 10639</t>
+          <t>1182; 10340</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 5183</t>
+          <t>0; 4995</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2483; 9780</t>
+          <t>2548; 9738</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8832; 21978</t>
+          <t>8860; 22555</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>23647; 43902</t>
+          <t>22864; 43534</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2037; 10781</t>
+          <t>2072; 10793</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>7363; 19578</t>
+          <t>6994; 19353</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3226; 12953</t>
+          <t>3025; 12689</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 6802</t>
+          <t>0; 7089</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 6048</t>
+          <t>0; 6202</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3262; 12990</t>
+          <t>3034; 12494</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 6701</t>
+          <t>0; 5688</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 9342</t>
+          <t>0; 8742</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 5818</t>
+          <t>0; 5115</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>677; 7993</t>
+          <t>681; 8135</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4129; 14760</t>
+          <t>4244; 14627</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1196; 12974</t>
+          <t>1218; 12803</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>919; 7818</t>
+          <t>949; 8352</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>4851; 16726</t>
+          <t>5237; 17318</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>29670; 51103</t>
+          <t>30208; 50354</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>49496; 77841</t>
+          <t>48742; 76648</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20213; 40504</t>
+          <t>20451; 40329</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>33598; 60830</t>
+          <t>34267; 61139</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>4963; 17783</t>
+          <t>4703; 17075</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6941; 23649</t>
+          <t>6561; 23133</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8146; 22882</t>
+          <t>7920; 21957</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>10073; 25071</t>
+          <t>10027; 24561</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>37066; 63918</t>
+          <t>36767; 62093</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>60244; 94567</t>
+          <t>59450; 94118</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>31716; 56626</t>
+          <t>31690; 57225</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>49842; 81321</t>
+          <t>47614; 78884</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15B_3_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P15B_3_R-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,35; 81,08</t>
+          <t>20,16; 81,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,67; 24,27</t>
+          <t>2,66; 25,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,47; 46,78</t>
+          <t>5,56; 45,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,32; 28,34</t>
+          <t>3,9; 31,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,88</t>
+          <t>0,0; 21,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,13; 38,4</t>
+          <t>8,29; 37,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,5; 19,45</t>
+          <t>3,34; 20,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,66; 54,16</t>
+          <t>11,06; 55,82</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,23; 19,67</t>
+          <t>4,22; 18,63</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,14; 35,1</t>
+          <t>12,09; 36,03</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,12; 20,45</t>
+          <t>5,57; 19,98</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -862,22 +862,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,72; 23,41</t>
+          <t>0,0; 21,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,22; 40,76</t>
+          <t>5,23; 39,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,15; 55,64</t>
+          <t>7,68; 48,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,6</t>
+          <t>0,0; 56,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,63</t>
+          <t>0,0; 44,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -897,22 +897,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,05</t>
+          <t>0,0; 34,6</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 12,07</t>
+          <t>1,47; 12,49</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,79; 30,61</t>
+          <t>5,57; 30,38</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,64; 22,81</t>
+          <t>2,48; 22,25</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>18,9%</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,59; 39,33</t>
+          <t>4,71; 39,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,34; 36,46</t>
+          <t>12,5; 34,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,11; 38,43</t>
+          <t>4,04; 38,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,55; 44,02</t>
+          <t>11,58; 49,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,14; 29,94</t>
+          <t>2,14; 29,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 31,67</t>
+          <t>3,95; 34,07</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,12; 21,28</t>
+          <t>8,05; 21,51</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 22,64</t>
+          <t>2,56; 25,6</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,78; 29,77</t>
+          <t>9,94; 32,48</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>25,03%</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,63; 51,32</t>
+          <t>11,41; 53,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,44</t>
+          <t>0,0; 18,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,85; 31,07</t>
+          <t>5,08; 31,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,25; 71,28</t>
+          <t>14,49; 67,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1167,32 +1167,32 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,15; 21,09</t>
+          <t>2,35; 21,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,12</t>
+          <t>0,0; 17,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,62; 36,1</t>
+          <t>6,62; 34,26</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,11</t>
+          <t>0,0; 14,01</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,8; 20,11</t>
+          <t>4,87; 19,91</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,85; 47,53</t>
+          <t>11,05; 47,52</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -1277,27 +1277,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,96; 86,58</t>
+          <t>11,19; 75,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,45; 62,21</t>
+          <t>8,17; 61,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,85; 63,19</t>
+          <t>9,0; 57,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,48</t>
+          <t>0,0; 51,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,52</t>
+          <t>0,0; 57,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 74,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1317,22 +1317,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,93; 56,51</t>
+          <t>7,12; 56,92</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,11; 25,61</t>
+          <t>3,22; 26,49</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,1; 54,11</t>
+          <t>6,92; 54,36</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,93</t>
+          <t>0,0; 54,06</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>13,5%</t>
         </is>
       </c>
     </row>
@@ -1417,32 +1417,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26,55; 90,86</t>
+          <t>25,89; 91,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,18; 39,69</t>
+          <t>8,66; 39,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,62; 32,61</t>
+          <t>3,63; 33,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,64; 45,54</t>
+          <t>12,2; 43,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,55</t>
+          <t>0,0; 48,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,78; 27,31</t>
+          <t>2,79; 28,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1452,27 +1452,27 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,94</t>
+          <t>0,0; 8,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,28; 59,91</t>
+          <t>13,91; 58,33</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,42; 27,95</t>
+          <t>8,68; 26,76</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,55; 14,08</t>
+          <t>1,6; 14,55</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,47; 28,2</t>
+          <t>6,95; 23,09</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>21,12; 59,99</t>
+          <t>21,43; 58,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31,1; 55,9</t>
+          <t>30,66; 55,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,98; 34,9</t>
+          <t>4,06; 37,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,01; 30,91</t>
+          <t>4,94; 26,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,46; 50,3</t>
+          <t>5,35; 48,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,02; 17,63</t>
+          <t>2,03; 17,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,23</t>
+          <t>0,0; 16,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,08; 19,43</t>
+          <t>4,64; 17,84</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19,39; 49,35</t>
+          <t>19,62; 47,11</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18,38; 34,99</t>
+          <t>19,26; 35,3</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,85; 20,05</t>
+          <t>3,81; 19,97</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,48; 20,69</t>
+          <t>6,3; 18,38</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,68%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11,46; 48,08</t>
+          <t>12,32; 48,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,52</t>
+          <t>0,0; 27,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,92</t>
+          <t>0,0; 18,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12,12; 49,93</t>
+          <t>10,19; 50,95</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,12</t>
+          <t>0,0; 23,43</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,54</t>
+          <t>0,0; 38,53</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,13</t>
+          <t>0,0; 20,05</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,38; 28,43</t>
+          <t>2,23; 28,16</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,96; 27,43</t>
+          <t>7,97; 28,35</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,47; 25,96</t>
+          <t>2,41; 23,47</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,55; 13,62</t>
+          <t>1,53; 13,35</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9,76; 32,29</t>
+          <t>10,4; 32,38</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,62%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>24,54; 40,91</t>
+          <t>24,28; 42,1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16,98; 26,71</t>
+          <t>17,04; 26,7</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10,34; 20,39</t>
+          <t>10,14; 20,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17,21; 30,7</t>
+          <t>16,94; 30,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,01; 18,2</t>
+          <t>4,76; 18,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,57; 9,06</t>
+          <t>2,74; 9,02</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,14; 11,47</t>
+          <t>4,23; 11,91</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,69; 11,5</t>
+          <t>4,59; 11,32</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16,95; 28,63</t>
+          <t>17,34; 28,92</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10,96; 17,35</t>
+          <t>11,15; 17,12</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8,14; 14,7</t>
+          <t>8,42; 15,08</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11,54; 19,11</t>
+          <t>11,51; 18,72</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>3695</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2908</t>
+          <t>2925</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>6620</t>
         </is>
       </c>
     </row>
@@ -2209,22 +2209,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1892; 7536</t>
+          <t>1874; 7536</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1359; 8989</t>
+          <t>983; 9594</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1242; 8985</t>
+          <t>1067; 8785</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>932; 7962</t>
+          <t>1054; 8438</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2234,37 +2234,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 6321</t>
+          <t>0; 5990</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2153; 11593</t>
+          <t>2501; 11377</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1015; 5637</t>
+          <t>1017; 6152</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1746; 8872</t>
+          <t>1812; 9144</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2735; 12715</t>
+          <t>2728; 12045</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5501; 17339</t>
+          <t>5971; 17799</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2923; 11672</t>
+          <t>3200; 11485</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5653</t>
+          <t>5598</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5653</t>
+          <t>5598</t>
         </is>
       </c>
     </row>
@@ -2422,22 +2422,22 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>870; 7496</t>
+          <t>0; 6985</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>959; 7483</t>
+          <t>960; 7292</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1983; 13544</t>
+          <t>1898; 12061</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5253</t>
+          <t>0; 5044</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6134</t>
+          <t>0; 6991</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2457,22 +2457,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 5893</t>
+          <t>0; 5818</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>888; 7518</t>
+          <t>916; 7780</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1982; 10480</t>
+          <t>1905; 10401</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1525; 13162</t>
+          <t>1472; 13221</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4831</t>
+          <t>6144</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3122</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8124</t>
+          <t>9265</t>
         </is>
       </c>
     </row>
@@ -2625,22 +2625,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>837; 7170</t>
+          <t>858; 7113</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7578; 19269</t>
+          <t>6609; 18216</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>956; 8928</t>
+          <t>939; 9035</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1823; 9389</t>
+          <t>2583; 11124</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2660,27 +2660,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>574; 8021</t>
+          <t>573; 7967</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>849; 7104</t>
+          <t>887; 7643</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6674; 19953</t>
+          <t>7548; 20165</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>928; 8402</t>
+          <t>951; 9502</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3746; 14327</t>
+          <t>4872; 15921</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10313</t>
+          <t>11154</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>732</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11017</t>
+          <t>11886</t>
         </is>
       </c>
     </row>
@@ -2833,22 +2833,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1893; 9143</t>
+          <t>2033; 9534</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5857</t>
+          <t>0; 5862</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1862; 11928</t>
+          <t>1949; 11937</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4096; 16930</t>
+          <t>4070; 19004</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2863,32 +2863,32 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>783; 7671</t>
+          <t>854; 7992</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4757</t>
+          <t>0; 3409</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1827; 9966</t>
+          <t>1827; 9459</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 5959</t>
+          <t>0; 6895</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3591; 15037</t>
+          <t>3645; 14884</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4552; 19945</t>
+          <t>5248; 22568</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>1006</t>
         </is>
       </c>
     </row>
@@ -3041,27 +3041,27 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>875; 6337</t>
+          <t>819; 5544</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1113; 8194</t>
+          <t>1076; 8101</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>896; 6397</t>
+          <t>912; 5820</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3947</t>
+          <t>0; 3839</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3397</t>
+          <t>0; 4502</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4533</t>
+          <t>0; 3357</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -3081,22 +3081,22 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1049; 8547</t>
+          <t>1077; 8609</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1026; 8444</t>
+          <t>1060; 8735</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1041; 7930</t>
+          <t>1014; 7967</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 3897</t>
+          <t>0; 4333</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7385</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>544</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7928</t>
+          <t>7311</t>
         </is>
       </c>
     </row>
@@ -3249,32 +3249,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2361; 8080</t>
+          <t>2303; 8148</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2787; 12046</t>
+          <t>2629; 11991</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>992; 8940</t>
+          <t>995; 9085</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3291; 11855</t>
+          <t>3174; 11260</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4299</t>
+          <t>0; 5111</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>983; 9671</t>
+          <t>989; 10007</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -3284,27 +3284,27 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 2683</t>
+          <t>0; 2318</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3174; 11679</t>
+          <t>2712; 11371</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5538; 18379</t>
+          <t>5708; 17600</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>993; 8996</t>
+          <t>1021; 9295</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3962; 14952</t>
+          <t>3762; 12505</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6893</t>
+          <t>7066</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>5691</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>12235</t>
+          <t>12758</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5764; 16369</t>
+          <t>5848; 15947</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>20449; 36753</t>
+          <t>20162; 36349</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1052; 9225</t>
+          <t>1072; 9787</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2611; 13429</t>
+          <t>2754; 14533</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1557; 9262</t>
+          <t>984; 8853</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1182; 10340</t>
+          <t>1189; 10183</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 4995</t>
+          <t>0; 4595</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2548; 9738</t>
+          <t>2709; 10426</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8860; 22555</t>
+          <t>8968; 21530</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>22864; 43534</t>
+          <t>23955; 43910</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2072; 10793</t>
+          <t>2053; 10751</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6994; 19353</t>
+          <t>7196; 20992</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7176</t>
+          <t>8076</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>3555</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>10158</t>
+          <t>11631</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3025; 12689</t>
+          <t>3252; 12884</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 7089</t>
+          <t>0; 6483</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 6202</t>
+          <t>0; 6282</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3034; 12494</t>
+          <t>2898; 14494</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 5688</t>
+          <t>0; 6310</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 8742</t>
+          <t>0; 9752</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 5115</t>
+          <t>0; 5360</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>681; 8135</t>
+          <t>755; 9526</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4244; 14627</t>
+          <t>4249; 15116</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1218; 12803</t>
+          <t>1190; 11577</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>949; 8352</t>
+          <t>937; 8192</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>5237; 17318</t>
+          <t>6476; 20161</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>46487</t>
+          <t>49506</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>15772</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>62259</t>
+          <t>66076</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>30208; 50354</t>
+          <t>29880; 51811</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>48742; 76648</t>
+          <t>48908; 76630</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20451; 40329</t>
+          <t>20044; 40235</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>34267; 61139</t>
+          <t>37246; 66343</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>4703; 17075</t>
+          <t>4464; 16998</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6561; 23133</t>
+          <t>7005; 23025</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7920; 21957</t>
+          <t>8102; 22800</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>10027; 24561</t>
+          <t>10660; 26274</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>36767; 62093</t>
+          <t>37616; 62717</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>59450; 94118</t>
+          <t>60449; 92848</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>31690; 57225</t>
+          <t>32791; 58691</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>47614; 78884</t>
+          <t>52043; 84630</t>
         </is>
       </c>
     </row>
